--- a/data/trans_orig/P44D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,62 +1453,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4321</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24589</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,62 +2139,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5069</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,62 +2482,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5313</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33956</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -3133,97 +3133,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6571</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>2202</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6586</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6392</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6131</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78482</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96463</t>
+          <t>97078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>174988</t>
+          <t>173799</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>198254</t>
+          <t>198286</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2016 (tasa de respuesta: 93,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -4398,97 +4398,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1083</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4483</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4488</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>79,74%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>42250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -5462,62 +5462,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5772</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>38993</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55527</t>
+          <t>55330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66008</t>
+          <t>66125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124505</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>143002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87776</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>102213</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>218177</t>
+          <t>218730</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>241362</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>64851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71858</t>
+          <t>71846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30167</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34679</t>
+          <t>34694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97766</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105929</t>
+          <t>105938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61055</t>
+          <t>61126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>38343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97901</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48830</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55501</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>97897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107382</t>
+          <t>107152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47303</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54425</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92444</t>
+          <t>93250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>103272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64535</t>
+          <t>64477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68746</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78769</t>
+          <t>79258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93672</t>
+          <t>94209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>101059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109867</t>
+          <t>110025</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183312</t>
+          <t>183455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200824</t>
+          <t>201777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>33567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339956</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>372149</t>
+          <t>371739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118600</t>
+          <t>118946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126522</t>
+          <t>126216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>467325</t>
+          <t>466167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>499594</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83117</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113303</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>696046</t>
+          <t>696505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>757529</t>
+          <t>757430</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>435534</t>
+          <t>435406</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>451549</t>
+          <t>451964</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1145284</t>
+          <t>1145091</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1212045</t>
+          <t>1212921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35610</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>173799</t>
+          <t>173042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>198286</t>
+          <t>198781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42250</t>
+          <t>42034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38993</t>
+          <t>38984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55330</t>
+          <t>54796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66125</t>
+          <t>65295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32337</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124820</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143002</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>102259</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>218730</t>
+          <t>218851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>241483</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69481</t>
+          <t>69211</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64851</t>
+          <t>64870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71846</t>
+          <t>71504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>102613</t>
+          <t>103398</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>98706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105938</t>
+          <t>106713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61126</t>
+          <t>63358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>35936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38343</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>93566</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>91988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98145</t>
+          <t>103685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>108247</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>108247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>108247</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>52091</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>47179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52877</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>103429</t>
+          <t>103829</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97897</t>
+          <t>98009</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107152</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>53956</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43215</t>
+          <t>48573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>56086</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>51960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>59415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99177</t>
+          <t>110042</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>103888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103272</t>
+          <t>115277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>124042</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>124042</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>124042</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>419</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -8858,27 +8858,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8893,27 +8893,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26410</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>743</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,27 +9163,27 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>37311</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,27 +9236,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>67145</t>
+          <t>66525</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64477</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68762</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>44417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>86993</t>
+          <t>100873</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79258</t>
+          <t>91878</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94209</t>
+          <t>107987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>106188</t>
+          <t>125103</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101059</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110025</t>
+          <t>129852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>193181</t>
+          <t>225976</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183455</t>
+          <t>214730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>201777</t>
+          <t>235153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107436</t>
+          <t>123737</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>107436</t>
+          <t>123737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107436</t>
+          <t>123737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>222136</t>
+          <t>259147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>222136</t>
+          <t>259147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>222136</t>
+          <t>259147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37271</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>363652</t>
+          <t>133286</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>126066</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>371739</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>123175</t>
+          <t>140680</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118946</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126216</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>486828</t>
+          <t>273967</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>466167</t>
+          <t>265530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>280064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>373331</t>
+          <t>143819</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>373331</t>
+          <t>143819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>373331</t>
+          <t>143819</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>503438</t>
+          <t>292383</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>503438</t>
+          <t>292383</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>503438</t>
+          <t>292383</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113496</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>727230</t>
+          <t>517627</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>696505</t>
+          <t>503935</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>757430</t>
+          <t>530724</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>444142</t>
+          <t>491496</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>435406</t>
+          <t>480907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>451964</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1171373</t>
+          <t>1009123</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1145091</t>
+          <t>993124</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1212921</t>
+          <t>1024126</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
